--- a/docs/traceability_report/ethfw_Traceability_Report.xlsx
+++ b/docs/traceability_report/ethfw_Traceability_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20400"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a0490934\tools\bidi-bq\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513B05C9-3D1B-4342-BEFA-E2A158C3BCC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4393BDBA-DB50-4EA7-912C-1F41E09538AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,16 +22,16 @@
     <sheet name="Template Revision History" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backward Traceability'!$A$1:$F$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backward Traceability'!$A$1:$F$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coverage Summary'!$A$1:$E$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Forward Traceability'!$A$1:$F$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Forward Traceability'!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="267">
   <si>
     <t>TI Information - Selective Disclosure</t>
   </si>
@@ -99,13 +99,13 @@
     <t>Report generated on</t>
   </si>
   <si>
-    <t>ETHFW-2377</t>
+    <t>ETHFW-2525</t>
   </si>
   <si>
     <t>ETHFW</t>
   </si>
   <si>
-    <t>2023-07-26 08:04:40.714625-05:00 CDT</t>
+    <t>2023-11-28 07:40:10.547725-06:00 CDT</t>
   </si>
   <si>
     <t>Forward Coverage Type</t>
@@ -132,7 +132,7 @@
     <t>Software Product Specification (SPS) -&gt; Test Case</t>
   </si>
   <si>
-    <t>91.67%</t>
+    <t>92.59%</t>
   </si>
   <si>
     <t>Test Case -&gt; Software Product Specification (SPS)</t>
@@ -165,486 +165,615 @@
     <t>Unit</t>
   </si>
   <si>
+    <t>JACINTOREQ-378</t>
+  </si>
+  <si>
+    <t>ETHFW-1290,ETHFW-955,ETHFW-1168,ETHFW-1245,ETHFW-1280,ETHFW-1170,ETHFW-1184,ETHFW-1237,ETHFW-1148,ETHFW-1143,ETHFW-1288</t>
+  </si>
+  <si>
+    <t>ETHFW-1290</t>
+  </si>
+  <si>
+    <t>ETHFW-1355</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4611</t>
+  </si>
+  <si>
+    <t>ETHFW-1290,ETHFW-937,ETHFW-1713,ETHFW-955,ETHFW-1196,ETHFW-1168,ETHFW-1718,ETHFW-1119,ETHFW-1245,ETHFW-1179,ETHFW-1947,ETHFW-1255,ETHFW-899,ETHFW-903,ETHFW-843,ETHFW-1280,ETHFW-1253,ETHFW-1232,ETHFW-1287,ETHFW-1170,ETHFW-1110,ETHFW-1302,ETHFW-1742,ETHFW-1184,ETHFW-1277,ETHFW-1711,ETHFW-1237,ETHFW-1856,ETHFW-1143,ETHFW-1154,ETHFW-1721,ETHFW-1203,ETHFW-1288,ETHFW-1716</t>
+  </si>
+  <si>
+    <t>ETHFW-1712</t>
+  </si>
+  <si>
+    <t>ETHFW-1900,ETHFW-1899</t>
+  </si>
+  <si>
+    <t>Unit,Unit</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>ETHFW-607</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1102</t>
+  </si>
+  <si>
+    <t>ETHFW-1712,ETHFW-1711</t>
+  </si>
+  <si>
+    <t>ETHFW-937</t>
+  </si>
+  <si>
+    <t>ETHFW-1344</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3524</t>
+  </si>
+  <si>
+    <t>ETHFW-1713</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7032</t>
+  </si>
+  <si>
+    <t>ETHFW-955</t>
+  </si>
+  <si>
+    <t>ETHFW-1405</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-550</t>
+  </si>
+  <si>
+    <t>ETHFW-1211</t>
+  </si>
+  <si>
+    <t>ETHFW-1887,ETHFW-1886</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-903</t>
+  </si>
+  <si>
+    <t>ETHFW-1739</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-906</t>
+  </si>
+  <si>
+    <t>ETHFW-1196</t>
+  </si>
+  <si>
+    <t>ETHFW-1399</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-380</t>
+  </si>
+  <si>
+    <t>ETHFW-937,ETHFW-955,ETHFW-899,ETHFW-903,ETHFW-843,ETHFW-941</t>
+  </si>
+  <si>
+    <t>ETHFW-1168</t>
+  </si>
+  <si>
+    <t>ETHFW-1058</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-818</t>
+  </si>
+  <si>
+    <t>ETHFW-1718</t>
+  </si>
+  <si>
+    <t>ETHFW-1823</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3549</t>
+  </si>
+  <si>
+    <t>ETHFW-1211,ETHFW-1739,ETHFW-1726</t>
+  </si>
+  <si>
+    <t>ETHFW-2489</t>
+  </si>
+  <si>
+    <t>ETHFW-2520</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-493</t>
+  </si>
+  <si>
+    <t>ETHFW-1211,ETHFW-1739</t>
+  </si>
+  <si>
+    <t>ETHFW-1193</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7047</t>
+  </si>
+  <si>
+    <t>ETHFW-1119</t>
+  </si>
+  <si>
+    <t>ETHFW-1547</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-240</t>
+  </si>
+  <si>
+    <t>ETHFW-1196,ETHFW-1255,ETHFW-1232,ETHFW-1110,ETHFW-1302,ETHFW-1277,ETHFW-1154</t>
+  </si>
+  <si>
+    <t>ETHFW-1726</t>
+  </si>
+  <si>
+    <t>ETHFW-1895</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1212</t>
+  </si>
+  <si>
+    <t>ETHFW-1245</t>
+  </si>
+  <si>
+    <t>ETHFW-1030</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7465</t>
+  </si>
+  <si>
+    <t>ETHFW-2489,ETHFW-2480,ETHFW-2477,ETHFW-2478,ETHFW-2479</t>
+  </si>
+  <si>
+    <t>ETHFW-1179</t>
+  </si>
+  <si>
+    <t>ETHFW-1664</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3547</t>
+  </si>
+  <si>
+    <t>ETHFW-1193,ETHFW-1740</t>
+  </si>
+  <si>
+    <t>ETHFW-1947</t>
+  </si>
+  <si>
+    <t>ETHFW-2009,ETHFW-2010</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-494</t>
+  </si>
+  <si>
+    <t>ETHFW-1255</t>
+  </si>
+  <si>
+    <t>ETHFW-1419</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7046</t>
+  </si>
+  <si>
+    <t>ETHFW-899</t>
+  </si>
+  <si>
+    <t>ETHFW-1325</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-547</t>
+  </si>
+  <si>
+    <t>ETHFW-1119,ETHFW-1253,ETHFW-1229,ETHFW-1203</t>
+  </si>
+  <si>
+    <t>ETHFW-903</t>
+  </si>
+  <si>
+    <t>ETHFW-1415,ETHFW-1927,ETHFW-1928,ETHFW-1930,ETHFW-1931,ETHFW-1932</t>
+  </si>
+  <si>
+    <t>Unit,Integration,Integration,Integration,Integration,Integration</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-678</t>
+  </si>
+  <si>
+    <t>ETHFW-843</t>
+  </si>
+  <si>
+    <t>ETHFW-1427</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1356</t>
+  </si>
+  <si>
+    <t>ETHFW-1878</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-546</t>
+  </si>
+  <si>
+    <t>ETHFW-1280</t>
+  </si>
+  <si>
+    <t>ETHFW-1094</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1378</t>
+  </si>
+  <si>
+    <t>ETHFW-1253</t>
+  </si>
+  <si>
+    <t>ETHFW-1545</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-2619</t>
+  </si>
+  <si>
+    <t>ETHFW-2480</t>
+  </si>
+  <si>
+    <t>ETHFW-2524</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-549</t>
+  </si>
+  <si>
+    <t>ETHFW-1287,ETHFW-1293</t>
+  </si>
+  <si>
+    <t>ETHFW-1232</t>
+  </si>
+  <si>
+    <t>ETHFW-1401</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3522</t>
+  </si>
+  <si>
+    <t>ETHFW-1293</t>
+  </si>
+  <si>
+    <t>ETHFW-1287</t>
+  </si>
+  <si>
+    <t>ETHFW-1542</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7030</t>
+  </si>
+  <si>
+    <t>ETHFW-2477</t>
+  </si>
+  <si>
+    <t>ETHFW-2521,ETHFW-2522</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1168</t>
+  </si>
+  <si>
+    <t>ETHFW-1742</t>
+  </si>
+  <si>
+    <t>ETHFW-1170</t>
+  </si>
+  <si>
+    <t>ETHFW-1330</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-551</t>
+  </si>
+  <si>
+    <t>ETHFW-1273</t>
+  </si>
+  <si>
+    <t>ETHFW-1110</t>
+  </si>
+  <si>
+    <t>ETHFW-1326</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4970</t>
+  </si>
+  <si>
+    <t>ETHFW-2225</t>
+  </si>
+  <si>
+    <t>ETHFW-1302</t>
+  </si>
+  <si>
+    <t>ETHFW-1323</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7395</t>
+  </si>
+  <si>
+    <t>ETHFW-1551</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1528</t>
+  </si>
+  <si>
+    <t>ETHFW-1856</t>
+  </si>
+  <si>
+    <t>ETHFW-1740</t>
+  </si>
+  <si>
+    <t>ETHFW-1886,ETHFW-1887</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3525</t>
+  </si>
+  <si>
+    <t>ETHFW-1229</t>
+  </si>
+  <si>
+    <t>ETHFW-1823,ETHFW-1701</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-7033</t>
+  </si>
+  <si>
+    <t>ETHFW-1184</t>
+  </si>
+  <si>
+    <t>ETHFW-1097</t>
+  </si>
+  <si>
     <t>JACINTOREQ-1166</t>
   </si>
   <si>
-    <t>ETHFW-1716,ETHFW-1721</t>
+    <t>ETHFW-1721,ETHFW-1716</t>
+  </si>
+  <si>
+    <t>ETHFW-1834</t>
+  </si>
+  <si>
+    <t>ETHFW-1277</t>
+  </si>
+  <si>
+    <t>ETHFW-1342</t>
+  </si>
+  <si>
+    <t>ETHFW-2464,ETHFW-2466,ETHFW-2465,ETHFW-2470,ETHFW-2472,ETHFW-2468,ETHFW-2471,ETHFW-2469,ETHFW-2467</t>
+  </si>
+  <si>
+    <t>Unit,Unit,Unit,Unit,Unit,Unit,Unit,Unit,Unit</t>
+  </si>
+  <si>
+    <t>ETHFW-1711</t>
+  </si>
+  <si>
+    <t>ETHFW-1237</t>
+  </si>
+  <si>
+    <t>ETHFW-2367</t>
+  </si>
+  <si>
+    <t>ETHFW-1148</t>
+  </si>
+  <si>
+    <t>ETHFW-987</t>
+  </si>
+  <si>
+    <t>ETHFW-941</t>
+  </si>
+  <si>
+    <t>ETHFW-1424</t>
+  </si>
+  <si>
+    <t>ETHFW-2478</t>
+  </si>
+  <si>
+    <t>ETHFW-2519</t>
+  </si>
+  <si>
+    <t>ETHFW-2479</t>
+  </si>
+  <si>
+    <t>ETHFW-2523</t>
+  </si>
+  <si>
+    <t>ETHFW-1552</t>
+  </si>
+  <si>
+    <t>ETHFW-1143</t>
+  </si>
+  <si>
+    <t>ETHFW-1025</t>
+  </si>
+  <si>
+    <t>ETHFW-1154</t>
+  </si>
+  <si>
+    <t>ETHFW-1362</t>
+  </si>
+  <si>
+    <t>ETHFW-1721</t>
+  </si>
+  <si>
+    <t>ETHFW-1203</t>
+  </si>
+  <si>
+    <t>ETHFW-1331</t>
+  </si>
+  <si>
+    <t>ETHFW-1288</t>
+  </si>
+  <si>
+    <t>ETHFW-1010</t>
   </si>
   <si>
     <t>ETHFW-1716</t>
   </si>
   <si>
-    <t>ETHFW-1823</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>ETHFW-1716,ETHFW-903,ETHFW-1742,ETHFW-1253,ETHFW-1196,ETHFW-1711,ETHFW-1143,ETHFW-955,ETHFW-1721,ETHFW-1302,ETHFW-1203,ETHFW-843,ETHFW-937,ETHFW-1110,ETHFW-1713,ETHFW-1170,ETHFW-1237,ETHFW-1168,ETHFW-1290,ETHFW-1154,ETHFW-1255,ETHFW-1856,ETHFW-1245,ETHFW-1184,ETHFW-1947,ETHFW-1232,ETHFW-1288,ETHFW-1287,ETHFW-1718,ETHFW-1277,ETHFW-1280,ETHFW-1179,ETHFW-1119,ETHFW-899</t>
-  </si>
-  <si>
-    <t>ETHFW-903</t>
-  </si>
-  <si>
-    <t>ETHFW-1415,ETHFW-1927,ETHFW-1928,ETHFW-1930,ETHFW-1931,ETHFW-1932</t>
-  </si>
-  <si>
-    <t>Unit,Integration,Integration,Integration,Integration,Integration</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-380</t>
-  </si>
-  <si>
-    <t>ETHFW-903,ETHFW-941,ETHFW-955,ETHFW-843,ETHFW-937,ETHFW-899</t>
-  </si>
-  <si>
-    <t>ETHFW-941</t>
-  </si>
-  <si>
-    <t>ETHFW-1424</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1168</t>
-  </si>
-  <si>
-    <t>ETHFW-1742</t>
-  </si>
-  <si>
-    <t>ETHFW-1823,ETHFW-1701</t>
-  </si>
-  <si>
-    <t>Unit,Unit</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-547</t>
-  </si>
-  <si>
-    <t>ETHFW-1253,ETHFW-1229,ETHFW-1203,ETHFW-1119</t>
-  </si>
-  <si>
-    <t>ETHFW-1253</t>
-  </si>
-  <si>
-    <t>ETHFW-1545</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-240</t>
-  </si>
-  <si>
-    <t>ETHFW-1196,ETHFW-1302,ETHFW-1110,ETHFW-1154,ETHFW-1255,ETHFW-1232,ETHFW-1277</t>
-  </si>
-  <si>
-    <t>ETHFW-1196</t>
-  </si>
-  <si>
-    <t>ETHFW-1399</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1102</t>
+    <t>MRD ID(s)</t>
+  </si>
+  <si>
+    <t>Test Case ID</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-378,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>ETHFW-1932</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1102,JACINTOREQ-3524,JACINTOREQ-7032</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-550,JACINTOREQ-903,JACINTOREQ-906</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-380,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4611,JACINTOREQ-7334,JACINTOREQ-818</t>
+  </si>
+  <si>
+    <t>ETHFW-1415</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-378,JACINTOREQ-380,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>ETHFW-1948</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3549,JACINTOREQ-493,JACINTOREQ-7047</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-240,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1212,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3547,JACINTOREQ-494,JACINTOREQ-7046</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4611,JACINTOREQ-547,JACINTOREQ-678,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1356,JACINTOREQ-3549,JACINTOREQ-7047</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4611,JACINTOREQ-546,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1378,JACINTOREQ-2619</t>
+  </si>
+  <si>
+    <t>ETHFW-2466</t>
+  </si>
+  <si>
+    <t>ETHFW-1886</t>
+  </si>
+  <si>
+    <t>ETHFW-1112,ETHFW-1739,ETHFW-1211,ETHFW-1193</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4611,JACINTOREQ-547,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>ETHFW-2467</t>
+  </si>
+  <si>
+    <t>ETHFW-2468</t>
+  </si>
+  <si>
+    <t>ETHFW-2469</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4611,JACINTOREQ-549,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>ETHFW-1887</t>
+  </si>
+  <si>
+    <t>ETHFW-1112,ETHFW-1211,ETHFW-1739,ETHFW-1193</t>
+  </si>
+  <si>
+    <t>ETHFW-2470</t>
+  </si>
+  <si>
+    <t>ETHFW-2464</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-3522,JACINTOREQ-549,JACINTOREQ-7030</t>
+  </si>
+  <si>
+    <t>ETHFW-2471</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1168,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>ETHFW-2521</t>
+  </si>
+  <si>
+    <t>ETHFW-2472</t>
+  </si>
+  <si>
+    <t>ETHFW-2522</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-4970,JACINTOREQ-7395</t>
+  </si>
+  <si>
+    <t>ETHFW-607,ETHFW-1920</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1102,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>JACINTOREQ-1528,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
+    <t>ETHFW-1899</t>
+  </si>
+  <si>
+    <t>ETHFW-1958,ETHFW-1711</t>
+  </si>
+  <si>
+    <t>ETHFW-1900</t>
   </si>
   <si>
     <t>ETHFW-1711,ETHFW-1712</t>
   </si>
   <si>
-    <t>ETHFW-1711</t>
-  </si>
-  <si>
-    <t>ETHFW-1900,ETHFW-1899</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3547</t>
-  </si>
-  <si>
-    <t>ETHFW-1193,ETHFW-1740</t>
-  </si>
-  <si>
-    <t>ETHFW-1193</t>
-  </si>
-  <si>
-    <t>ETHFW-1887,ETHFW-1886</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-494</t>
-  </si>
-  <si>
-    <t>ETHFW-1143</t>
-  </si>
-  <si>
-    <t>ETHFW-1025</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-378</t>
-  </si>
-  <si>
-    <t>ETHFW-1143,ETHFW-955,ETHFW-1170,ETHFW-1237,ETHFW-1148,ETHFW-1168,ETHFW-1290,ETHFW-1245,ETHFW-1184,ETHFW-1288,ETHFW-1280</t>
-  </si>
-  <si>
-    <t>ETHFW-1229</t>
-  </si>
-  <si>
-    <t>ETHFW-1552</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3525</t>
-  </si>
-  <si>
-    <t>ETHFW-1211</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3549</t>
-  </si>
-  <si>
-    <t>ETHFW-1211,ETHFW-1726,ETHFW-1739</t>
-  </si>
-  <si>
-    <t>ETHFW-955</t>
-  </si>
-  <si>
-    <t>ETHFW-1405</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-493</t>
-  </si>
-  <si>
-    <t>ETHFW-1211,ETHFW-1739</t>
-  </si>
-  <si>
-    <t>ETHFW-1721</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1356</t>
-  </si>
-  <si>
-    <t>ETHFW-1726</t>
-  </si>
-  <si>
-    <t>ETHFW-1302</t>
-  </si>
-  <si>
-    <t>ETHFW-1323</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3524</t>
-  </si>
-  <si>
-    <t>ETHFW-1712</t>
-  </si>
-  <si>
-    <t>ETHFW-1895</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-550</t>
-  </si>
-  <si>
-    <t>ETHFW-607</t>
-  </si>
-  <si>
-    <t>ETHFW-1203</t>
-  </si>
-  <si>
-    <t>ETHFW-1331</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-903</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-906</t>
-  </si>
-  <si>
-    <t>ETHFW-843</t>
-  </si>
-  <si>
-    <t>ETHFW-1427</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-551</t>
-  </si>
-  <si>
-    <t>ETHFW-1273</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-818</t>
-  </si>
-  <si>
-    <t>ETHFW-1713</t>
-  </si>
-  <si>
-    <t>ETHFW-937</t>
-  </si>
-  <si>
-    <t>ETHFW-1344</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1528</t>
-  </si>
-  <si>
-    <t>ETHFW-1856</t>
-  </si>
-  <si>
-    <t>ETHFW-1834</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-549</t>
-  </si>
-  <si>
-    <t>ETHFW-1287,ETHFW-1293</t>
-  </si>
-  <si>
-    <t>ETHFW-1110</t>
-  </si>
-  <si>
-    <t>ETHFW-1326</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1212</t>
-  </si>
-  <si>
-    <t>ETHFW-1718</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-546</t>
-  </si>
-  <si>
-    <t>ETHFW-1179</t>
-  </si>
-  <si>
-    <t>ETHFW-1739</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-678</t>
-  </si>
-  <si>
-    <t>ETHFW-1119</t>
-  </si>
-  <si>
-    <t>ETHFW-1170</t>
-  </si>
-  <si>
-    <t>ETHFW-1330</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1378</t>
-  </si>
-  <si>
-    <t>ETHFW-1878</t>
-  </si>
-  <si>
-    <t>ETHFW-1740</t>
-  </si>
-  <si>
-    <t>ETHFW-1886,ETHFW-1887</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-2619</t>
-  </si>
-  <si>
-    <t>ETHFW-1237</t>
-  </si>
-  <si>
-    <t>ETHFW-2367</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3522</t>
-  </si>
-  <si>
-    <t>ETHFW-1293</t>
-  </si>
-  <si>
-    <t>ETHFW-1148</t>
-  </si>
-  <si>
-    <t>ETHFW-987</t>
-  </si>
-  <si>
-    <t>ETHFW-1168</t>
-  </si>
-  <si>
-    <t>ETHFW-1058</t>
-  </si>
-  <si>
-    <t>ETHFW-1290</t>
-  </si>
-  <si>
-    <t>ETHFW-1355</t>
-  </si>
-  <si>
-    <t>ETHFW-1154</t>
-  </si>
-  <si>
-    <t>ETHFW-1362</t>
-  </si>
-  <si>
-    <t>ETHFW-1255</t>
-  </si>
-  <si>
-    <t>ETHFW-1419</t>
-  </si>
-  <si>
-    <t>ETHFW-1245</t>
-  </si>
-  <si>
-    <t>ETHFW-1030</t>
-  </si>
-  <si>
-    <t>ETHFW-1184</t>
-  </si>
-  <si>
-    <t>ETHFW-1097</t>
-  </si>
-  <si>
-    <t>ETHFW-1947</t>
-  </si>
-  <si>
-    <t>ETHFW-2009,ETHFW-2010</t>
-  </si>
-  <si>
-    <t>ETHFW-1232</t>
-  </si>
-  <si>
-    <t>ETHFW-1401</t>
-  </si>
-  <si>
-    <t>ETHFW-1288</t>
-  </si>
-  <si>
-    <t>ETHFW-1010</t>
-  </si>
-  <si>
-    <t>ETHFW-1287</t>
-  </si>
-  <si>
-    <t>ETHFW-1542</t>
-  </si>
-  <si>
-    <t>ETHFW-1277</t>
-  </si>
-  <si>
-    <t>ETHFW-1342</t>
-  </si>
-  <si>
-    <t>ETHFW-1280</t>
-  </si>
-  <si>
-    <t>ETHFW-1094</t>
-  </si>
-  <si>
-    <t>ETHFW-1664</t>
-  </si>
-  <si>
-    <t>ETHFW-1547</t>
-  </si>
-  <si>
-    <t>ETHFW-899</t>
-  </si>
-  <si>
-    <t>ETHFW-1325</t>
-  </si>
-  <si>
-    <t>ETHFW-1551</t>
-  </si>
-  <si>
-    <t>MRD ID(s)</t>
-  </si>
-  <si>
-    <t>Test Case ID</t>
-  </si>
-  <si>
-    <t>ETHFW-1932</t>
-  </si>
-  <si>
-    <t>Integration</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1166,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-380,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>ETHFW-1948</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1168,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>ETHFW-1415</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-4611,JACINTOREQ-547</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-240,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1102,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3547,JACINTOREQ-494</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-378,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3525,JACINTOREQ-547</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-3549,JACINTOREQ-493</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-378,JACINTOREQ-380,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1356,JACINTOREQ-3549</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1102,JACINTOREQ-3524</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-550,JACINTOREQ-903,JACINTOREQ-906</t>
-  </si>
-  <si>
-    <t>ETHFW-1886</t>
-  </si>
-  <si>
-    <t>ETHFW-1112,ETHFW-1739,ETHFW-1211,ETHFW-1193</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-4611,JACINTOREQ-818</t>
-  </si>
-  <si>
-    <t>ETHFW-1887</t>
-  </si>
-  <si>
-    <t>ETHFW-1112,ETHFW-1211,ETHFW-1739,ETHFW-1193</t>
-  </si>
-  <si>
-    <t>ETHFW-607,ETHFW-1920</t>
-  </si>
-  <si>
-    <t>ETHFW-1899</t>
-  </si>
-  <si>
-    <t>ETHFW-1958,ETHFW-1711</t>
-  </si>
-  <si>
-    <t>ETHFW-1900</t>
-  </si>
-  <si>
     <t>ETHFW-2009</t>
   </si>
   <si>
     <t>ETHFW-1952</t>
   </si>
   <si>
+    <t>JACINTOREQ-3525,JACINTOREQ-547,JACINTOREQ-7033</t>
+  </si>
+  <si>
+    <t>ETHFW-2465</t>
+  </si>
+  <si>
     <t>ETHFW-2010</t>
   </si>
   <si>
-    <t>JACINTOREQ-1528,JACINTOREQ-4611</t>
-  </si>
-  <si>
     <t>ETHFW-1927</t>
   </si>
   <si>
+    <t>JACINTOREQ-1166,JACINTOREQ-4611,JACINTOREQ-7334</t>
+  </si>
+  <si>
     <t>ETHFW-1930</t>
   </si>
   <si>
@@ -660,27 +789,9 @@
     <t>ETHFW-1686</t>
   </si>
   <si>
-    <t>JACINTOREQ-4611,JACINTOREQ-549</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1212,JACINTOREQ-4611</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-4611,JACINTOREQ-546</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-4611,JACINTOREQ-547,JACINTOREQ-678</t>
-  </si>
-  <si>
-    <t>JACINTOREQ-1378,JACINTOREQ-2619</t>
-  </si>
-  <si>
     <t>ETHFW-1966,ETHFW-1716,ETHFW-1742</t>
   </si>
   <si>
-    <t>JACINTOREQ-3522,JACINTOREQ-549</t>
-  </si>
-  <si>
     <t>Coverage Type</t>
   </si>
   <si>
@@ -714,13 +825,13 @@
     <t>Initial version</t>
   </si>
   <si>
+    <t>Not a testable case, ETHFW makes all OS calls via OSAL layer, verified by code inspection</t>
+  </si>
+  <si>
     <t>This feature is not testable on TI EVMs, only docs update are done.</t>
   </si>
   <si>
     <t>This is just a documentation update, cannot be tested.</t>
-  </si>
-  <si>
-    <t>Not a testable case, ETHFW makes all OS calls via OSAL layer, verified by code inspection</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1457,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -1389,7 +1500,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>44</v>
       </c>
@@ -1425,19 +1536,19 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>43</v>
@@ -1445,53 +1556,49 @@
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="B7" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>43</v>
@@ -1499,107 +1606,107 @@
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>43</v>
@@ -1607,49 +1714,53 @@
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>43</v>
@@ -1657,125 +1768,125 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>101</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>43</v>
@@ -1783,85 +1894,85 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>43</v>
@@ -1869,139 +1980,179 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="C31" s="1"/>
       <c r="D31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="F32" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>145</v>
+      </c>
       <c r="C33" s="1"/>
       <c r="D33" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="A34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="C34" s="1"/>
       <c r="D34" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
+      <c r="A35" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="C35" s="1"/>
       <c r="D35" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+        <v>134</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>155</v>
+      </c>
       <c r="C36" s="1"/>
       <c r="D36" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="C37" s="1"/>
       <c r="D37" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="C38" s="1"/>
       <c r="D38" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>165</v>
+      </c>
       <c r="C39" s="1"/>
       <c r="D39" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>43</v>
@@ -2012,41 +2163,41 @@
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="2" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2054,10 +2205,10 @@
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>43</v>
@@ -2068,10 +2219,10 @@
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>43</v>
@@ -2082,10 +2233,10 @@
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="2" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>43</v>
@@ -2096,34 +2247,34 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="1"/>
+        <v>178</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>43</v>
@@ -2134,24 +2285,104 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>43</v>
       </c>
     </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="A1:F55" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -2163,11 +2394,11 @@
         <v>37</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="3" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>39</v>
@@ -2185,61 +2416,61 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>173</v>
+        <v>43</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>199</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>43</v>
@@ -2248,664 +2479,664 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="2" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="2" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="2" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>186</v>
+        <v>96</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2" t="s">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="2" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="2" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="2" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="2" t="s">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="2" t="s">
-        <v>190</v>
+        <v>47</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>191</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="2" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="2" t="s">
-        <v>136</v>
+        <v>215</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="2" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>219</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="2" t="s">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="2" t="s">
-        <v>99</v>
+        <v>222</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="2" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="2" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="2" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="2" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="2" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>173</v>
+        <v>43</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="2" t="s">
-        <v>164</v>
+        <v>82</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="2" t="s">
-        <v>204</v>
+        <v>136</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>173</v>
+        <v>43</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>48</v>
+        <v>195</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="2" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>173</v>
+        <v>43</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="2" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="2" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>43</v>
@@ -2914,122 +3145,340 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="2" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>211</v>
+        <v>72</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="2" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="2" t="s">
-        <v>103</v>
+        <v>236</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="2" t="s">
-        <v>47</v>
+        <v>238</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>43</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="D48" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
+      <c r="D49" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>252</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F49" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:F62" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3046,24 +3495,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3071,10 +3520,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>227</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -3082,21 +3531,21 @@
         <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>155</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3114,30 +3563,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>222</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>225</v>
+        <v>262</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>226</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>

--- a/docs/traceability_report/ethfw_Traceability_Report.xlsx
+++ b/docs/traceability_report/ethfw_Traceability_Report.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table of Contents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Script Input Parameters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Coverage Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Forward Traceability" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Backward Traceability" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Traceability Deviations" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Template Revision History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table of Contents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Script Input Parameters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forward Traceability" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backward Traceability" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Deviations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Template Revision History" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'Coverage Summary'!$A$1:$E$3</definedName>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">'Forward Traceability'!$A$1:$F$4</definedName>
-    <definedName hidden="1" localSheetId="4" name="_xlnm._FilterDatabase">'Backward Traceability'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Coverage Summary'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Forward Traceability'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Backward Traceability'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -77,39 +77,39 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -473,9 +473,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="10"/>
-    <col customWidth="1" max="2" min="2" width="35"/>
-    <col customWidth="1" max="3" min="3" width="80"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Copyright (C) 2024 Texas Instruments Incorporated</t>
+          <t>Copyright (C) 2025 Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
@@ -625,10 +625,10 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -641,9 +641,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="20"/>
-    <col customWidth="1" max="2" min="2" width="20"/>
-    <col customWidth="1" max="3" min="3" width="35"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2900</t>
+          <t>ETHFW-3041</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2024-11-26 07:22:00.299041-06:00 CDT</t>
+          <t>2025-02-18 03:22:26.036870-06:00 CDT</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -694,10 +694,10 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="60"/>
-    <col customWidth="1" max="2" min="2" width="22"/>
-    <col customWidth="1" max="4" min="4" width="60"/>
-    <col customWidth="1" max="5" min="5" width="22"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E3"/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -781,14 +781,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="20"/>
-    <col customWidth="1" max="2" min="2" width="20"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
-    <col customWidth="1" max="5" min="5" width="20"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -822,78 +822,422 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>JACINTOREQ-2621</t>
+          <t>JACINTOREQ-7796</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1199</t>
+          <t>ETHFW-3007,ETHFW-3008,ETHFW-3009</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-1199</t>
+          <t>ETHFW-3007</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2908</t>
+          <t>ETHFW-3032</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>JACINTOREQ-554</t>
+          <t>JACINTOREQ-6571</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1199</t>
+          <t>ETHFW-2213,ETHFW-2208</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
+          <t>ETHFW-2213</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2917,ETHFW-2913,ETHFW-2914,ETHFW-2915,ETHFW-2916</t>
+          <t>ETHFW-3030</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Validation,Validation,Validation,Validation,Validation</t>
+          <t>Validation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>JACINTOREQ-4908</t>
+          <t>JACINTOREQ-6575</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
+          <t>ETHFW-2204,ETHFW-2207,ETHFW-2206</t>
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2204</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6570</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2201,ETHFW-2202,ETHFW-2211,ETHFW-2199,ETHFW-2203</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2201</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6623</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2459,ETHFW-2724</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2459</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3038</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-7921</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3010,ETHFW-3011</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2208</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-7662</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2723</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3010</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3035</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3008</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3031</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n"/>
+      <c r="B10" s="3" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3011</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3036</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n"/>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2207</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2724</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3039</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2206</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2202</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2211</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2199</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3037</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2203</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3030</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3009</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3033</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2723</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-3040</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <autoFilter ref="A1:F19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -903,14 +1247,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="20"/>
-    <col customWidth="1" max="2" min="2" width="20"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
-    <col customWidth="1" max="5" min="5" width="20"/>
-    <col customWidth="1" max="6" min="6" width="20"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -944,46 +1288,46 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-1199</t>
+          <t>ETHFW-3007</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>JACINTOREQ-2621,JACINTOREQ-554</t>
+          <t>JACINTOREQ-7796</t>
         </is>
       </c>
       <c r="C2" s="3" t="n"/>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2908</t>
+          <t>ETHFW-3030</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-1199</t>
+          <t>ETHFW-2206,ETHFW-2213,ETHFW-2202,ETHFW-2204,ETHFW-2203,ETHFW-2211,ETHFW-2208,ETHFW-2207,ETHFW-2201</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
+          <t>ETHFW-2213</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>JACINTOREQ-4908</t>
+          <t>JACINTOREQ-6571</t>
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2913</t>
+          <t>ETHFW-3031</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -993,17 +1337,25 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
+          <t>ETHFW-3008</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2204</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6575</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2914</t>
+          <t>ETHFW-3032</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -1013,17 +1365,25 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
+          <t>ETHFW-3007</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2201</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6570</t>
+        </is>
+      </c>
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2915</t>
+          <t>ETHFW-3033</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1033,17 +1393,25 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
+          <t>ETHFW-3009</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2459</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6623</t>
+        </is>
+      </c>
       <c r="C6" s="3" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2916</t>
+          <t>ETHFW-3035</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1053,17 +1421,25 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
+          <t>ETHFW-3010</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2208</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6571</t>
+        </is>
+      </c>
       <c r="C7" s="3" t="n"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ETHFW-2917</t>
+          <t>ETHFW-3036</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1073,13 +1449,253 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ETHFW-2718</t>
-        </is>
-      </c>
+          <t>ETHFW-3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3010</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-7921</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3037</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2199</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3008</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-7796</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3038</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2459</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3011</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-7921</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3039</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2724</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2207</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6575</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3040</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ETHFW-2723</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2724</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6623</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2206</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6575</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2202</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6570</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2211</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6570</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2199</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6570</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2203</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-6570</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-3009</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-7796</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
+      <c r="F18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>ETHFW-2723</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>JACINTOREQ-7662</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <autoFilter ref="A1:F19"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1092,9 +1708,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="60"/>
-    <col customWidth="1" max="2" min="2" width="20"/>
-    <col customWidth="1" max="3" min="3" width="80"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1120,7 +1736,7 @@
       <c r="C2" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1133,10 +1749,10 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="20"/>
-    <col customWidth="1" max="2" min="2" width="20"/>
-    <col customWidth="1" max="3" min="3" width="20"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1184,6 +1800,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>